--- a/docs/bulk-templates/tasks_recee_sample.xlsx
+++ b/docs/bulk-templates/tasks_recee_sample.xlsx
@@ -603,7 +603,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Store the recee is for (must exist), e.g. ST-001.</t>
+          <t>Mandatory. Store the recee is for (must exist), e.g. ST-001.</t>
         </is>
       </c>
     </row>

--- a/docs/bulk-templates/tasks_recee_sample.xlsx
+++ b/docs/bulk-templates/tasks_recee_sample.xlsx
@@ -450,7 +450,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -461,7 +461,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>store_uid</t>
+          <t>customer_code</t>
         </is>
       </c>
     </row>
@@ -473,7 +473,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>ST-101</t>
+          <t>YG000000026</t>
         </is>
       </c>
     </row>
@@ -485,7 +485,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>ST-106</t>
+          <t>YG000101109</t>
         </is>
       </c>
     </row>
@@ -497,7 +497,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>ST-104</t>
+          <t>YG000000038</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>ST-102</t>
+          <t>YG000000033</t>
         </is>
       </c>
     </row>
@@ -521,7 +521,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>ST-105</t>
+          <t>YG000101108</t>
         </is>
       </c>
     </row>
@@ -533,7 +533,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>ST-103</t>
+          <t>YG000000037</t>
         </is>
       </c>
     </row>
@@ -551,7 +551,7 @@
   <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
   </cols>
@@ -593,7 +593,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>store_uid</t>
+          <t>customer_code</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -603,7 +603,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Mandatory. Store the recee is for (must exist), e.g. ST-001.</t>
+          <t>Mandatory. Customer Code of the store the recee is for (must exist).</t>
         </is>
       </c>
     </row>

--- a/docs/bulk-templates/tasks_recee_sample.xlsx
+++ b/docs/bulk-templates/tasks_recee_sample.xlsx
@@ -456,12 +456,12 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>vendor_uid</t>
+          <t>VENDOR_UID</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>customer_code</t>
+          <t>CUSTOMER_CODE</t>
         </is>
       </c>
     </row>
@@ -576,7 +576,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>vendor_uid</t>
+          <t>VENDOR_UID</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -593,7 +593,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>customer_code</t>
+          <t>CUSTOMER_CODE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">

--- a/docs/bulk-templates/tasks_recee_sample.xlsx
+++ b/docs/bulk-templates/tasks_recee_sample.xlsx
@@ -73,12 +73,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -548,66 +551,76 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="60" customHeight="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Column</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
-        <is>
-          <t>Required</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Notes</t>
+          <t>Column names are matched on SPELLING ONLY. Upper or lower case makes no difference, and spaces, hyphens and underscores are treated the same - so CUST_CD, Cust_CD and "cust cd" are the same column. The headers on the Data sheet are all-caps; keep the wording, and the case is up to you. A sheet filled in with Caps Lock on uploads exactly like any other. Do not rename, reorder or delete columns - only the wording identifies them.</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
           <t>VENDOR_UID</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Vendor the task is for (must exist), e.g. VND-001.</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>CUSTOMER_CODE</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Mandatory. Customer Code of the store the recee is for (must exist).</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>